--- a/datosfinales.xlsx
+++ b/datosfinales.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17220" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$O$848</definedName>
@@ -653,7 +653,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G2" s="2" t="n"/>
@@ -702,7 +702,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G3" s="2" t="n"/>
@@ -751,7 +751,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G4" s="2" t="n"/>
@@ -845,7 +845,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G6" s="2" t="n"/>
@@ -935,7 +935,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G8" s="2" t="n"/>
@@ -984,7 +984,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G9" s="2" t="n"/>
@@ -1164,7 +1164,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G13" s="2" t="n"/>
@@ -1258,7 +1258,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G15" s="2" t="n"/>
@@ -1356,7 +1356,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G17" s="2" t="n"/>
@@ -1405,7 +1405,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G18" s="2" t="n"/>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G21" s="2" t="n"/>
@@ -1642,7 +1642,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G23" s="2" t="n"/>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G25" s="2" t="n"/>
@@ -1781,7 +1781,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G26" s="2" t="n"/>
@@ -1830,7 +1830,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G27" s="2" t="n"/>
@@ -1961,7 +1961,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G30" s="2" t="n"/>
@@ -2215,7 +2215,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G36" s="2" t="n"/>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G41" s="2" t="n"/>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G43" s="2" t="n"/>
@@ -2575,7 +2575,7 @@
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>2025-02-04</t>
+          <t>404</t>
         </is>
       </c>
       <c r="G44" s="3" t="n"/>
@@ -2665,7 +2665,7 @@
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G46" s="3" t="n"/>
@@ -2714,7 +2714,7 @@
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G47" s="3" t="n"/>
@@ -2763,7 +2763,7 @@
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G48" s="3" t="n"/>
@@ -2812,7 +2812,7 @@
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G49" s="3" t="n"/>
@@ -2943,7 +2943,7 @@
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G52" s="3" t="n"/>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="G53" s="3" t="n"/>
@@ -3221,7 +3221,7 @@
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G58" s="3" t="n"/>
@@ -3270,7 +3270,7 @@
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G59" s="3" t="n"/>
@@ -3319,7 +3319,7 @@
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G60" s="3" t="n"/>
@@ -3368,7 +3368,7 @@
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G61" s="3" t="n"/>
@@ -3499,7 +3499,7 @@
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G64" s="3" t="n"/>
@@ -3591,7 +3591,7 @@
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G66" s="3" t="n"/>
@@ -3677,7 +3677,7 @@
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G68" s="4" t="n"/>
@@ -3869,7 +3869,7 @@
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G72" s="4" t="n"/>
@@ -4159,7 +4159,7 @@
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G78" s="4" t="n"/>
@@ -4461,7 +4461,7 @@
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G84" s="4" t="n"/>
@@ -5016,7 +5016,7 @@
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G95" s="4" t="n"/>
@@ -5445,7 +5445,7 @@
       </c>
       <c r="F104" s="4" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G104" s="4" t="n"/>
@@ -5837,7 +5837,7 @@
       </c>
       <c r="F112" s="4" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G112" s="4" t="n"/>
@@ -7021,7 +7021,7 @@
       </c>
       <c r="F136" s="4" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G136" s="4" t="n"/>
@@ -7421,7 +7421,7 @@
       </c>
       <c r="F144" s="4" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G144" s="4" t="n"/>
@@ -8160,7 +8160,7 @@
       </c>
       <c r="F159" s="4" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G159" s="4" t="n"/>
@@ -8315,7 +8315,7 @@
       </c>
       <c r="F162" s="4" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G162" s="4" t="n"/>
@@ -9291,7 +9291,7 @@
       </c>
       <c r="F182" s="4" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="G182" s="4" t="n"/>
@@ -9446,7 +9446,7 @@
       </c>
       <c r="F185" s="4" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G185" s="4" t="n"/>
@@ -9642,7 +9642,7 @@
       </c>
       <c r="F189" s="4" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G189" s="4" t="n"/>
@@ -9740,7 +9740,7 @@
       </c>
       <c r="F191" s="4" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G191" s="4" t="n"/>
@@ -9797,7 +9797,7 @@
       </c>
       <c r="F192" s="4" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G192" s="4" t="n"/>
@@ -10621,7 +10621,7 @@
       </c>
       <c r="F208" s="4" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G208" s="4" t="n"/>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="F215" s="4" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G215" s="4" t="n"/>
@@ -11176,7 +11176,7 @@
       </c>
       <c r="F219" s="4" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="G219" s="4" t="n"/>
@@ -11833,7 +11833,7 @@
       </c>
       <c r="F232" s="4" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G232" s="4" t="n"/>
@@ -12380,7 +12380,7 @@
       </c>
       <c r="F243" s="4" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G243" s="4" t="n"/>
@@ -12486,7 +12486,7 @@
       </c>
       <c r="F245" s="4" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G245" s="4" t="n"/>
@@ -12539,7 +12539,7 @@
       </c>
       <c r="F246" s="4" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G246" s="4" t="n"/>
@@ -12637,7 +12637,7 @@
       </c>
       <c r="F248" s="4" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G248" s="4" t="n"/>
@@ -12743,7 +12743,7 @@
       </c>
       <c r="F250" s="4" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G250" s="4" t="n"/>
@@ -12955,7 +12955,7 @@
       </c>
       <c r="F254" s="4" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G254" s="4" t="n"/>
@@ -14588,7 +14588,7 @@
       </c>
       <c r="F287" s="4" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G287" s="4" t="n"/>
@@ -14743,7 +14743,7 @@
       </c>
       <c r="F290" s="4" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G290" s="4" t="n"/>
@@ -15282,7 +15282,7 @@
       </c>
       <c r="F301" s="4" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G301" s="4" t="n"/>
@@ -15694,7 +15694,7 @@
       </c>
       <c r="F309" s="4" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G309" s="4" t="n"/>
@@ -15935,7 +15935,7 @@
       </c>
       <c r="F314" s="4" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G314" s="4" t="n"/>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="F321" s="4" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G321" s="4" t="n"/>
@@ -16486,7 +16486,7 @@
       </c>
       <c r="F325" s="4" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>404</t>
         </is>
       </c>
       <c r="G325" s="4" t="n"/>
@@ -16792,7 +16792,7 @@
       </c>
       <c r="F331" s="4" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="G331" s="4" t="n"/>
@@ -16898,7 +16898,7 @@
       </c>
       <c r="F333" s="4" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G333" s="4" t="n"/>
@@ -17053,7 +17053,7 @@
       </c>
       <c r="F336" s="4" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="G336" s="4" t="n"/>
@@ -17159,7 +17159,7 @@
       </c>
       <c r="F338" s="4" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G338" s="4" t="n"/>
@@ -18460,7 +18460,7 @@
       </c>
       <c r="F363" s="4" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G363" s="4" t="n"/>
@@ -18566,7 +18566,7 @@
       </c>
       <c r="F365" s="4" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G365" s="4" t="n"/>
@@ -19023,7 +19023,7 @@
       </c>
       <c r="F374" s="4" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G374" s="4" t="n"/>
@@ -19235,7 +19235,7 @@
       </c>
       <c r="F378" s="4" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G378" s="4" t="n"/>
@@ -19476,7 +19476,7 @@
       </c>
       <c r="F383" s="4" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G383" s="4" t="n"/>
@@ -19631,7 +19631,7 @@
       </c>
       <c r="F386" s="4" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G386" s="4" t="n"/>
@@ -20880,7 +20880,7 @@
       </c>
       <c r="F411" s="4" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="G411" s="4" t="n"/>
@@ -21908,7 +21908,7 @@
       </c>
       <c r="F435" s="5" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G435" s="5" t="n"/>
@@ -21961,7 +21961,7 @@
       </c>
       <c r="F436" s="5" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G436" s="5" t="n"/>
@@ -23679,7 +23679,7 @@
       </c>
       <c r="F478" s="5" t="inlineStr">
         <is>
-          <t>2026-01-25</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G478" s="5" t="n"/>
@@ -24450,7 +24450,7 @@
       </c>
       <c r="F497" s="5" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="G497" s="5" t="n"/>
@@ -24618,7 +24618,7 @@
       </c>
       <c r="F501" s="5" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G501" s="5" t="n"/>
@@ -25062,7 +25062,7 @@
       </c>
       <c r="F513" s="5" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G513" s="5" t="n"/>
@@ -25431,7 +25431,7 @@
       </c>
       <c r="F522" s="5" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="G522" s="5" t="n"/>
@@ -25521,7 +25521,7 @@
       </c>
       <c r="F524" s="5" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G524" s="5" t="n"/>
@@ -25948,7 +25948,7 @@
       </c>
       <c r="F535" s="5" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G535" s="5" t="n"/>
@@ -26559,7 +26559,7 @@
       </c>
       <c r="F550" s="5" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G550" s="5" t="n"/>
@@ -27962,7 +27962,7 @@
       </c>
       <c r="F585" s="5" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>404</t>
         </is>
       </c>
       <c r="G585" s="5" t="n"/>
@@ -28788,7 +28788,7 @@
       </c>
       <c r="F607" s="5" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G607" s="5" t="n"/>
@@ -29103,7 +29103,7 @@
       </c>
       <c r="F614" s="5" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G614" s="5" t="n"/>
@@ -29444,7 +29444,7 @@
       </c>
       <c r="F623" s="5" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G623" s="5" t="n"/>
@@ -29953,7 +29953,7 @@
       </c>
       <c r="F636" s="5" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G636" s="5" t="n"/>
@@ -30064,7 +30064,7 @@
       </c>
       <c r="F639" s="5" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="G639" s="5" t="n"/>
@@ -31294,7 +31294,7 @@
       </c>
       <c r="F669" s="5" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="G669" s="5" t="n"/>
@@ -31828,7 +31828,7 @@
       </c>
       <c r="F683" s="5" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G683" s="5" t="n"/>
@@ -31873,7 +31873,7 @@
       </c>
       <c r="F684" s="5" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G684" s="5" t="n"/>
@@ -33103,7 +33103,7 @@
       </c>
       <c r="F714" s="6" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G714" s="6" t="n"/>
@@ -33185,7 +33185,7 @@
       </c>
       <c r="F716" s="6" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G716" s="6" t="n"/>
@@ -33230,7 +33230,7 @@
       </c>
       <c r="F717" s="6" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G717" s="6" t="n"/>
@@ -33320,7 +33320,7 @@
       </c>
       <c r="F719" s="6" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G719" s="6" t="n"/>
@@ -33484,7 +33484,7 @@
       </c>
       <c r="F723" s="6" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G723" s="6" t="n"/>
@@ -33529,7 +33529,7 @@
       </c>
       <c r="F724" s="6" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G724" s="6" t="inlineStr">
@@ -33539,7 +33539,7 @@
       </c>
       <c r="H724" s="6" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="I724" s="6" t="inlineStr">
@@ -33627,7 +33627,7 @@
       </c>
       <c r="F726" s="6" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G726" s="6" t="n"/>
@@ -33672,7 +33672,7 @@
       </c>
       <c r="F727" s="6" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G727" s="6" t="n"/>
@@ -33717,7 +33717,7 @@
       </c>
       <c r="F728" s="6" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G728" s="6" t="n"/>
@@ -35031,7 +35031,7 @@
       </c>
       <c r="F758" s="7" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G758" s="7" t="n"/>
@@ -36645,7 +36645,7 @@
       </c>
       <c r="F792" s="7" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G792" s="7" t="n"/>
@@ -37004,7 +37004,7 @@
       </c>
       <c r="F799" s="8" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G799" s="8" t="n"/>
@@ -37098,7 +37098,7 @@
       </c>
       <c r="F801" s="8" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G801" s="8" t="n"/>
@@ -37315,7 +37315,7 @@
       </c>
       <c r="F806" s="8" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G806" s="8" t="n"/>
@@ -37405,7 +37405,7 @@
       </c>
       <c r="F808" s="8" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G808" s="8" t="n"/>
@@ -37499,7 +37499,7 @@
       </c>
       <c r="F810" s="8" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G810" s="8" t="n"/>
@@ -37597,7 +37597,7 @@
       </c>
       <c r="F812" s="8" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G812" s="8" t="n"/>
@@ -37781,7 +37781,7 @@
       </c>
       <c r="F816" s="8" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G816" s="8" t="n"/>
@@ -37875,7 +37875,7 @@
       </c>
       <c r="F818" s="8" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G818" s="8" t="n"/>
@@ -37965,7 +37965,7 @@
       </c>
       <c r="F820" s="8" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G820" s="8" t="n"/>
@@ -38063,7 +38063,7 @@
       </c>
       <c r="F822" s="8" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G822" s="8" t="n"/>
@@ -38198,7 +38198,7 @@
       </c>
       <c r="F825" s="8" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G825" s="8" t="n"/>
@@ -38288,7 +38288,7 @@
       </c>
       <c r="F827" s="8" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G827" s="8" t="n"/>
@@ -38337,7 +38337,7 @@
       </c>
       <c r="F828" s="8" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G828" s="8" t="n"/>
@@ -38386,7 +38386,7 @@
       </c>
       <c r="F829" s="8" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G829" s="8" t="n"/>
@@ -38480,7 +38480,7 @@
       </c>
       <c r="F831" s="8" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G831" s="8" t="n"/>
@@ -38529,7 +38529,7 @@
       </c>
       <c r="F832" s="8" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G832" s="8" t="n"/>
@@ -38578,7 +38578,7 @@
       </c>
       <c r="F833" s="8" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G833" s="8" t="n"/>
@@ -38627,7 +38627,7 @@
       </c>
       <c r="F834" s="8" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G834" s="8" t="n"/>
@@ -38676,7 +38676,7 @@
       </c>
       <c r="F835" s="8" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G835" s="8" t="n"/>
@@ -38725,7 +38725,7 @@
       </c>
       <c r="F836" s="8" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G836" s="8" t="n"/>
@@ -38774,7 +38774,7 @@
       </c>
       <c r="F837" s="8" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G837" s="8" t="n"/>
@@ -38823,7 +38823,7 @@
       </c>
       <c r="F838" s="8" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G838" s="8" t="n"/>
@@ -38872,7 +38872,7 @@
       </c>
       <c r="F839" s="8" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G839" s="8" t="n"/>
@@ -39015,7 +39015,7 @@
       </c>
       <c r="F842" s="8" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G842" s="8" t="n"/>
@@ -39064,7 +39064,7 @@
       </c>
       <c r="F843" s="8" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G843" s="8" t="n"/>
@@ -39113,7 +39113,7 @@
       </c>
       <c r="F844" s="8" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G844" s="8" t="n"/>
@@ -39162,7 +39162,7 @@
       </c>
       <c r="F845" s="8" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G845" s="8" t="n"/>
@@ -39211,7 +39211,7 @@
       </c>
       <c r="F846" s="8" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G846" s="8" t="n"/>
@@ -39260,7 +39260,7 @@
       </c>
       <c r="F847" s="8" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G847" s="8" t="n"/>
@@ -39309,7 +39309,7 @@
       </c>
       <c r="F848" s="8" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G848" s="8" t="n"/>

--- a/datosfinales.xlsx
+++ b/datosfinales.xlsx
@@ -3581,8 +3581,10 @@
           <t>SiraRego</t>
         </is>
       </c>
-      <c r="D66" s="3" t="n">
-        <v>404</v>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>404</t>
+        </is>
       </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
@@ -8111,7 +8113,11 @@
           <t>rauldiaz_</t>
         </is>
       </c>
-      <c r="D158" s="4" t="n"/>
+      <c r="D158" s="4" t="inlineStr">
+        <is>
+          <t>404</t>
+        </is>
+      </c>
       <c r="E158" s="4" t="n"/>
       <c r="F158" s="4" t="n"/>
       <c r="G158" s="4" t="n"/>
@@ -12531,7 +12537,11 @@
           <t>m_barbero</t>
         </is>
       </c>
-      <c r="D246" s="4" t="n"/>
+      <c r="D246" s="4" t="inlineStr">
+        <is>
+          <t>404</t>
+        </is>
+      </c>
       <c r="E246" s="4" t="inlineStr">
         <is>
           <t>veronicambarbero.bsky.social</t>
@@ -16217,7 +16227,11 @@
           <t>oscarramis</t>
         </is>
       </c>
-      <c r="D320" s="4" t="n"/>
+      <c r="D320" s="4" t="inlineStr">
+        <is>
+          <t>404</t>
+        </is>
+      </c>
       <c r="E320" s="4" t="n"/>
       <c r="F320" s="4" t="n"/>
       <c r="G320" s="4" t="n"/>
@@ -19676,7 +19690,11 @@
           <t>MARSANCHEZSIERR</t>
         </is>
       </c>
-      <c r="D387" s="4" t="n"/>
+      <c r="D387" s="4" t="inlineStr">
+        <is>
+          <t>404</t>
+        </is>
+      </c>
       <c r="E387" s="4" t="n"/>
       <c r="F387" s="4" t="n"/>
       <c r="G387" s="4" t="n"/>
@@ -27215,7 +27233,11 @@
           <t>juanlobato_es</t>
         </is>
       </c>
-      <c r="D566" s="5" t="n"/>
+      <c r="D566" s="5" t="inlineStr">
+        <is>
+          <t>404</t>
+        </is>
+      </c>
       <c r="E566" s="5" t="inlineStr">
         <is>
           <t>juanlobato.bsky.social</t>
@@ -34222,7 +34244,11 @@
           <t>SeAcaboLaFiesta</t>
         </is>
       </c>
-      <c r="D741" s="6" t="n"/>
+      <c r="D741" s="6" t="inlineStr">
+        <is>
+          <t>404</t>
+        </is>
+      </c>
       <c r="E741" s="6" t="n"/>
       <c r="F741" s="6" t="n"/>
       <c r="G741" s="6" t="n"/>
@@ -35497,7 +35523,11 @@
           <t>mariachivite</t>
         </is>
       </c>
-      <c r="D768" s="7" t="n"/>
+      <c r="D768" s="7" t="inlineStr">
+        <is>
+          <t>404</t>
+        </is>
+      </c>
       <c r="E768" s="7" t="n"/>
       <c r="F768" s="7" t="n"/>
       <c r="G768" s="7" t="n"/>
@@ -38190,7 +38220,11 @@
           <t>ULPGC</t>
         </is>
       </c>
-      <c r="D825" s="8" t="n"/>
+      <c r="D825" s="8" t="inlineStr">
+        <is>
+          <t>404</t>
+        </is>
+      </c>
       <c r="E825" s="8" t="inlineStr">
         <is>
           <t>ulpgc.es</t>

--- a/datosfinales.xlsx
+++ b/datosfinales.xlsx
@@ -531,7 +531,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:O848"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="40" customWidth="1" min="2" max="2"/>
@@ -643,7 +643,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -653,7 +653,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G2" s="2" t="n"/>
@@ -692,7 +692,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -702,7 +702,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G3" s="2" t="n"/>
@@ -741,7 +741,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -751,7 +751,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G4" s="2" t="n"/>
@@ -790,7 +790,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -835,7 +835,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -845,7 +845,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G6" s="2" t="n"/>
@@ -884,7 +884,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E7" s="2" t="n"/>
@@ -925,7 +925,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -935,7 +935,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G8" s="2" t="n"/>
@@ -974,7 +974,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G9" s="2" t="n"/>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E10" s="2" t="n"/>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E11" s="2" t="n"/>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G13" s="2" t="n"/>
@@ -1201,11 +1201,7 @@
           <t>viviendagob</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>2026-02-14</t>
-        </is>
-      </c>
+      <c r="D14" s="2" t="n"/>
       <c r="E14" s="2" t="inlineStr">
         <is>
           <t>viviendagob.bsky.social</t>
@@ -1248,7 +1244,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1258,7 +1254,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G15" s="2" t="n"/>
@@ -1297,7 +1293,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1346,7 +1342,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1356,7 +1352,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G17" s="2" t="n"/>
@@ -1395,7 +1391,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2025-01-20</t>
+          <t>2025-01-21</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1405,7 +1401,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G18" s="2" t="n"/>
@@ -1444,7 +1440,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1489,7 +1485,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1534,7 +1530,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -1544,7 +1540,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G21" s="2" t="n"/>
@@ -1583,7 +1579,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1632,7 +1628,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1642,7 +1638,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G23" s="2" t="n"/>
@@ -1722,7 +1718,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1732,7 +1728,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G25" s="2" t="n"/>
@@ -1771,7 +1767,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1781,7 +1777,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G26" s="2" t="n"/>
@@ -1820,7 +1816,7 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -1830,7 +1826,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G27" s="2" t="n"/>
@@ -1910,7 +1906,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E29" s="2" t="n"/>
@@ -1951,7 +1947,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -1961,7 +1957,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G30" s="2" t="n"/>
@@ -2000,7 +1996,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E31" s="2" t="n"/>
@@ -2041,7 +2037,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E32" s="2" t="n"/>
@@ -2082,7 +2078,7 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E33" s="2" t="n"/>
@@ -2123,7 +2119,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E34" s="2" t="n"/>
@@ -2164,7 +2160,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E35" s="2" t="n"/>
@@ -2205,7 +2201,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -2215,7 +2211,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G36" s="2" t="n"/>
@@ -2254,7 +2250,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -2299,7 +2295,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E38" s="2" t="n"/>
@@ -2340,7 +2336,7 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E39" s="2" t="n"/>
@@ -2381,7 +2377,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -2426,7 +2422,7 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -2436,7 +2432,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G41" s="2" t="n"/>
@@ -2475,7 +2471,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E42" s="2" t="n"/>
@@ -2516,7 +2512,7 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -2526,7 +2522,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G43" s="2" t="n"/>
@@ -2565,7 +2561,7 @@
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
@@ -2614,7 +2610,7 @@
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E45" s="3" t="n"/>
@@ -2665,7 +2661,7 @@
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G46" s="3" t="n"/>
@@ -2714,7 +2710,7 @@
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G47" s="3" t="n"/>
@@ -2753,7 +2749,7 @@
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
@@ -2763,7 +2759,7 @@
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G48" s="3" t="n"/>
@@ -2802,7 +2798,7 @@
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
@@ -2812,7 +2808,7 @@
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G49" s="3" t="n"/>
@@ -2933,7 +2929,7 @@
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
@@ -2943,7 +2939,7 @@
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G52" s="3" t="n"/>
@@ -2982,7 +2978,7 @@
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
@@ -2992,7 +2988,7 @@
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G53" s="3" t="n"/>
@@ -3031,7 +3027,7 @@
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E54" s="3" t="n"/>
@@ -3072,7 +3068,7 @@
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E55" s="3" t="n"/>
@@ -3113,7 +3109,7 @@
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
@@ -3162,7 +3158,7 @@
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
@@ -3221,7 +3217,7 @@
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G58" s="3" t="n"/>
@@ -3260,7 +3256,7 @@
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
@@ -3270,7 +3266,7 @@
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G59" s="3" t="n"/>
@@ -3309,7 +3305,7 @@
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
@@ -3319,7 +3315,7 @@
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G60" s="3" t="n"/>
@@ -3368,7 +3364,7 @@
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G61" s="3" t="n"/>
@@ -3407,7 +3403,7 @@
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E62" s="3" t="n"/>
@@ -3448,7 +3444,7 @@
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E63" s="3" t="n"/>
@@ -3489,7 +3485,7 @@
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E64" s="3" t="inlineStr">
@@ -3499,7 +3495,7 @@
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G64" s="3" t="n"/>
@@ -3538,7 +3534,7 @@
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
@@ -3581,11 +3577,7 @@
           <t>SiraRego</t>
         </is>
       </c>
-      <c r="D66" s="3" t="inlineStr">
-        <is>
-          <t>404</t>
-        </is>
-      </c>
+      <c r="D66" s="3" t="n"/>
       <c r="E66" s="3" t="inlineStr">
         <is>
           <t>sirarego.bsky.social</t>
@@ -3593,7 +3585,7 @@
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G66" s="3" t="n"/>
@@ -3632,7 +3624,7 @@
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E67" s="4" t="n"/>
@@ -3669,7 +3661,7 @@
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr">
@@ -3679,7 +3671,7 @@
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G68" s="4" t="n"/>
@@ -3755,7 +3747,7 @@
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr">
@@ -3812,7 +3804,7 @@
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E71" s="4" t="n"/>
@@ -3861,7 +3853,7 @@
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr">
@@ -3871,7 +3863,7 @@
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="G72" s="4" t="n"/>
@@ -3918,7 +3910,7 @@
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E73" s="4" t="n"/>
@@ -4053,7 +4045,7 @@
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E76" s="4" t="n"/>
@@ -4102,7 +4094,7 @@
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E77" s="4" t="n"/>
@@ -4151,7 +4143,7 @@
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E78" s="4" t="inlineStr">
@@ -4161,7 +4153,7 @@
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G78" s="4" t="n"/>
@@ -4208,7 +4200,7 @@
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E79" s="4" t="n"/>
@@ -4253,7 +4245,7 @@
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E80" s="4" t="inlineStr">
@@ -4310,7 +4302,7 @@
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E81" s="4" t="n"/>
@@ -4359,7 +4351,7 @@
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E82" s="4" t="inlineStr">
@@ -4453,7 +4445,7 @@
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E84" s="4" t="inlineStr">
@@ -4463,7 +4455,7 @@
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G84" s="4" t="n"/>
@@ -4508,11 +4500,7 @@
           <t>pilaraliaa</t>
         </is>
       </c>
-      <c r="D85" s="4" t="inlineStr">
-        <is>
-          <t>2026-02-11</t>
-        </is>
-      </c>
+      <c r="D85" s="4" t="n"/>
       <c r="E85" s="4" t="n"/>
       <c r="F85" s="4" t="n"/>
       <c r="G85" s="4" t="n"/>
@@ -4559,7 +4547,7 @@
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E86" s="4" t="n"/>
@@ -4608,7 +4596,7 @@
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
@@ -4618,7 +4606,7 @@
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G87" s="4" t="n"/>
@@ -4665,7 +4653,7 @@
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E88" s="4" t="n"/>
@@ -4804,7 +4792,7 @@
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr">
@@ -4861,7 +4849,7 @@
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E92" s="4" t="n"/>
@@ -4910,7 +4898,7 @@
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E93" s="4" t="n"/>
@@ -4959,7 +4947,7 @@
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E94" s="4" t="n"/>
@@ -5008,7 +4996,7 @@
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E95" s="4" t="inlineStr">
@@ -5018,7 +5006,7 @@
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G95" s="4" t="n"/>
@@ -5061,7 +5049,7 @@
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="E96" s="4" t="inlineStr">
@@ -5114,7 +5102,7 @@
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E97" s="4" t="n"/>
@@ -5241,7 +5229,7 @@
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E100" s="4" t="inlineStr">
@@ -5298,7 +5286,7 @@
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E101" s="4" t="n"/>
@@ -5388,7 +5376,7 @@
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E103" s="4" t="n"/>
@@ -5437,7 +5425,7 @@
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E104" s="4" t="inlineStr">
@@ -5447,7 +5435,7 @@
       </c>
       <c r="F104" s="4" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G104" s="4" t="n"/>
@@ -5494,7 +5482,7 @@
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E105" s="4" t="n"/>
@@ -5543,7 +5531,7 @@
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E106" s="4" t="n"/>
@@ -5592,7 +5580,7 @@
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E107" s="4" t="n"/>
@@ -5723,7 +5711,7 @@
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E110" s="4" t="n"/>
@@ -5772,7 +5760,7 @@
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="E111" s="4" t="inlineStr">
@@ -5829,7 +5817,7 @@
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E112" s="4" t="inlineStr">
@@ -5839,7 +5827,7 @@
       </c>
       <c r="F112" s="4" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G112" s="4" t="n"/>
@@ -5882,7 +5870,7 @@
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E113" s="4" t="n"/>
@@ -5931,7 +5919,7 @@
       </c>
       <c r="D114" s="4" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E114" s="4" t="n"/>
@@ -5980,7 +5968,7 @@
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E115" s="4" t="n"/>
@@ -6066,7 +6054,7 @@
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E117" s="4" t="inlineStr">
@@ -6123,7 +6111,7 @@
       </c>
       <c r="D118" s="4" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E118" s="4" t="inlineStr">
@@ -6180,7 +6168,7 @@
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E119" s="4" t="inlineStr">
@@ -6237,7 +6225,7 @@
       </c>
       <c r="D120" s="4" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E120" s="4" t="n"/>
@@ -6286,7 +6274,7 @@
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E121" s="4" t="n"/>
@@ -6335,7 +6323,7 @@
       </c>
       <c r="D122" s="4" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E122" s="4" t="n"/>
@@ -6384,7 +6372,7 @@
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E123" s="4" t="n"/>
@@ -6433,7 +6421,7 @@
       </c>
       <c r="D124" s="4" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E124" s="4" t="n"/>
@@ -6482,7 +6470,7 @@
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E125" s="4" t="n"/>
@@ -6531,7 +6519,7 @@
       </c>
       <c r="D126" s="4" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E126" s="4" t="n"/>
@@ -6580,7 +6568,7 @@
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E127" s="4" t="n"/>
@@ -6678,7 +6666,7 @@
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E129" s="4" t="n"/>
@@ -6727,7 +6715,7 @@
       </c>
       <c r="D130" s="4" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E130" s="4" t="n"/>
@@ -6776,7 +6764,7 @@
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="E131" s="4" t="n"/>
@@ -6825,7 +6813,7 @@
       </c>
       <c r="D132" s="4" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="E132" s="4" t="n"/>
@@ -6874,7 +6862,7 @@
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E133" s="4" t="n"/>
@@ -6923,7 +6911,7 @@
       </c>
       <c r="D134" s="4" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E134" s="4" t="n"/>
@@ -7013,7 +7001,7 @@
       </c>
       <c r="D136" s="4" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="E136" s="4" t="inlineStr">
@@ -7023,7 +7011,7 @@
       </c>
       <c r="F136" s="4" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G136" s="4" t="n"/>
@@ -7201,7 +7189,7 @@
       </c>
       <c r="D140" s="4" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E140" s="4" t="n"/>
@@ -7250,7 +7238,7 @@
       </c>
       <c r="D141" s="4" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E141" s="4" t="inlineStr">
@@ -7307,7 +7295,7 @@
       </c>
       <c r="D142" s="4" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E142" s="4" t="n"/>
@@ -7356,7 +7344,7 @@
       </c>
       <c r="D143" s="4" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E143" s="4" t="inlineStr">
@@ -7413,7 +7401,7 @@
       </c>
       <c r="D144" s="4" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E144" s="4" t="inlineStr">
@@ -7470,7 +7458,7 @@
       </c>
       <c r="D145" s="4" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E145" s="4" t="n"/>
@@ -7519,7 +7507,7 @@
       </c>
       <c r="D146" s="4" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E146" s="4" t="n"/>
@@ -7609,7 +7597,7 @@
       </c>
       <c r="D148" s="4" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E148" s="4" t="n"/>
@@ -7658,7 +7646,7 @@
       </c>
       <c r="D149" s="4" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E149" s="4" t="n"/>
@@ -7703,7 +7691,7 @@
       </c>
       <c r="D150" s="4" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E150" s="4" t="n"/>
@@ -7752,7 +7740,7 @@
       </c>
       <c r="D151" s="4" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E151" s="4" t="inlineStr">
@@ -7809,7 +7797,7 @@
       </c>
       <c r="D152" s="4" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E152" s="4" t="n"/>
@@ -7858,7 +7846,7 @@
       </c>
       <c r="D153" s="4" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E153" s="4" t="n"/>
@@ -7907,7 +7895,7 @@
       </c>
       <c r="D154" s="4" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E154" s="4" t="inlineStr">
@@ -7960,7 +7948,7 @@
       </c>
       <c r="D155" s="4" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E155" s="4" t="n"/>
@@ -8009,7 +7997,7 @@
       </c>
       <c r="D156" s="4" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E156" s="4" t="n"/>
@@ -8058,7 +8046,7 @@
       </c>
       <c r="D157" s="4" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E157" s="4" t="inlineStr">
@@ -8113,11 +8101,7 @@
           <t>rauldiaz_</t>
         </is>
       </c>
-      <c r="D158" s="4" t="inlineStr">
-        <is>
-          <t>404</t>
-        </is>
-      </c>
+      <c r="D158" s="4" t="n"/>
       <c r="E158" s="4" t="n"/>
       <c r="F158" s="4" t="n"/>
       <c r="G158" s="4" t="n"/>
@@ -8166,7 +8150,7 @@
       </c>
       <c r="F159" s="4" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G159" s="4" t="n"/>
@@ -8213,7 +8197,7 @@
       </c>
       <c r="D160" s="4" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="E160" s="4" t="n"/>
@@ -8262,7 +8246,7 @@
       </c>
       <c r="D161" s="4" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E161" s="4" t="n"/>
@@ -8311,7 +8295,7 @@
       </c>
       <c r="D162" s="4" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E162" s="4" t="inlineStr">
@@ -8321,7 +8305,7 @@
       </c>
       <c r="F162" s="4" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G162" s="4" t="n"/>
@@ -8368,7 +8352,7 @@
       </c>
       <c r="D163" s="4" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E163" s="4" t="n"/>
@@ -8417,7 +8401,7 @@
       </c>
       <c r="D164" s="4" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E164" s="4" t="n"/>
@@ -8466,7 +8450,7 @@
       </c>
       <c r="D165" s="4" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E165" s="4" t="n"/>
@@ -8515,7 +8499,7 @@
       </c>
       <c r="D166" s="4" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E166" s="4" t="n"/>
@@ -8658,7 +8642,7 @@
       </c>
       <c r="D169" s="4" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E169" s="4" t="n"/>
@@ -8789,7 +8773,7 @@
       </c>
       <c r="D172" s="4" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E172" s="4" t="n"/>
@@ -8838,7 +8822,7 @@
       </c>
       <c r="D173" s="4" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E173" s="4" t="n"/>
@@ -8887,7 +8871,7 @@
       </c>
       <c r="D174" s="4" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E174" s="4" t="n"/>
@@ -8932,7 +8916,7 @@
       </c>
       <c r="D175" s="4" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E175" s="4" t="n"/>
@@ -8981,7 +8965,7 @@
       </c>
       <c r="D176" s="4" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E176" s="4" t="inlineStr">
@@ -9034,7 +9018,7 @@
       </c>
       <c r="D177" s="4" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="E177" s="4" t="inlineStr">
@@ -9044,7 +9028,7 @@
       </c>
       <c r="F177" s="4" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G177" s="4" t="n"/>
@@ -9091,7 +9075,7 @@
       </c>
       <c r="D178" s="4" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E178" s="4" t="n"/>
@@ -9181,7 +9165,7 @@
       </c>
       <c r="D180" s="4" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E180" s="4" t="inlineStr">
@@ -9287,7 +9271,7 @@
       </c>
       <c r="D182" s="4" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E182" s="4" t="inlineStr">
@@ -9344,7 +9328,7 @@
       </c>
       <c r="D183" s="4" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E183" s="4" t="n"/>
@@ -9393,7 +9377,7 @@
       </c>
       <c r="D184" s="4" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E184" s="4" t="n"/>
@@ -9442,7 +9426,7 @@
       </c>
       <c r="D185" s="4" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E185" s="4" t="inlineStr">
@@ -9452,7 +9436,7 @@
       </c>
       <c r="F185" s="4" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G185" s="4" t="n"/>
@@ -9499,7 +9483,7 @@
       </c>
       <c r="D186" s="4" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E186" s="4" t="n"/>
@@ -9548,7 +9532,7 @@
       </c>
       <c r="D187" s="4" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E187" s="4" t="n"/>
@@ -9638,7 +9622,7 @@
       </c>
       <c r="D189" s="4" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E189" s="4" t="inlineStr">
@@ -9648,7 +9632,7 @@
       </c>
       <c r="F189" s="4" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G189" s="4" t="n"/>
@@ -9695,7 +9679,7 @@
       </c>
       <c r="D190" s="4" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E190" s="4" t="n"/>
@@ -9793,7 +9777,7 @@
       </c>
       <c r="D192" s="4" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E192" s="4" t="inlineStr">
@@ -9803,7 +9787,7 @@
       </c>
       <c r="F192" s="4" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G192" s="4" t="n"/>
@@ -9850,7 +9834,7 @@
       </c>
       <c r="D193" s="4" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="E193" s="4" t="n"/>
@@ -9899,7 +9883,7 @@
       </c>
       <c r="D194" s="4" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E194" s="4" t="n"/>
@@ -9944,7 +9928,7 @@
       </c>
       <c r="D195" s="4" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E195" s="4" t="inlineStr">
@@ -10001,7 +9985,7 @@
       </c>
       <c r="D196" s="4" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E196" s="4" t="inlineStr">
@@ -10148,7 +10132,7 @@
       </c>
       <c r="D199" s="4" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E199" s="4" t="inlineStr">
@@ -10205,7 +10189,7 @@
       </c>
       <c r="D200" s="4" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E200" s="4" t="inlineStr">
@@ -10262,7 +10246,7 @@
       </c>
       <c r="D201" s="4" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E201" s="4" t="inlineStr">
@@ -10364,7 +10348,7 @@
       </c>
       <c r="D203" s="4" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E203" s="4" t="n"/>
@@ -10413,7 +10397,7 @@
       </c>
       <c r="D204" s="4" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E204" s="4" t="n"/>
@@ -10462,7 +10446,7 @@
       </c>
       <c r="D205" s="4" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E205" s="4" t="inlineStr">
@@ -10519,7 +10503,7 @@
       </c>
       <c r="D206" s="4" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="E206" s="4" t="n"/>
@@ -10568,7 +10552,7 @@
       </c>
       <c r="D207" s="4" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E207" s="4" t="n"/>
@@ -10617,7 +10601,7 @@
       </c>
       <c r="D208" s="4" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E208" s="4" t="inlineStr">
@@ -10627,7 +10611,7 @@
       </c>
       <c r="F208" s="4" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G208" s="4" t="n"/>
@@ -10674,7 +10658,7 @@
       </c>
       <c r="D209" s="4" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E209" s="4" t="n"/>
@@ -10723,7 +10707,7 @@
       </c>
       <c r="D210" s="4" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="E210" s="4" t="n"/>
@@ -10768,7 +10752,7 @@
       </c>
       <c r="D211" s="4" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E211" s="4" t="n"/>
@@ -10817,7 +10801,7 @@
       </c>
       <c r="D212" s="4" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E212" s="4" t="inlineStr">
@@ -10923,7 +10907,7 @@
       </c>
       <c r="D214" s="4" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E214" s="4" t="n"/>
@@ -10982,7 +10966,7 @@
       </c>
       <c r="F215" s="4" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G215" s="4" t="n"/>
@@ -11076,11 +11060,7 @@
           <t>teresajorda</t>
         </is>
       </c>
-      <c r="D217" s="4" t="inlineStr">
-        <is>
-          <t>2026-02-14</t>
-        </is>
-      </c>
+      <c r="D217" s="4" t="n"/>
       <c r="E217" s="4" t="inlineStr">
         <is>
           <t>teresajorda.bsky.social</t>
@@ -11172,7 +11152,7 @@
       </c>
       <c r="D219" s="4" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="E219" s="4" t="inlineStr">
@@ -11229,7 +11209,7 @@
       </c>
       <c r="D220" s="4" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E220" s="4" t="n"/>
@@ -11327,7 +11307,7 @@
       </c>
       <c r="D222" s="4" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E222" s="4" t="n"/>
@@ -11376,7 +11356,7 @@
       </c>
       <c r="D223" s="4" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E223" s="4" t="n"/>
@@ -11425,7 +11405,7 @@
       </c>
       <c r="D224" s="4" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E224" s="4" t="n"/>
@@ -11474,7 +11454,7 @@
       </c>
       <c r="D225" s="4" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E225" s="4" t="n"/>
@@ -11519,7 +11499,7 @@
       </c>
       <c r="D226" s="4" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E226" s="4" t="inlineStr">
@@ -11576,7 +11556,7 @@
       </c>
       <c r="D227" s="4" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E227" s="4" t="n"/>
@@ -11625,7 +11605,7 @@
       </c>
       <c r="D228" s="4" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E228" s="4" t="n"/>
@@ -11674,7 +11654,7 @@
       </c>
       <c r="D229" s="4" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="E229" s="4" t="n"/>
@@ -11723,7 +11703,7 @@
       </c>
       <c r="D230" s="4" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E230" s="4" t="inlineStr">
@@ -11780,7 +11760,7 @@
       </c>
       <c r="D231" s="4" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E231" s="4" t="n"/>
@@ -11829,7 +11809,7 @@
       </c>
       <c r="D232" s="4" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E232" s="4" t="inlineStr">
@@ -11839,7 +11819,7 @@
       </c>
       <c r="F232" s="4" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G232" s="4" t="n"/>
@@ -11886,7 +11866,7 @@
       </c>
       <c r="D233" s="4" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E233" s="4" t="n"/>
@@ -11935,7 +11915,7 @@
       </c>
       <c r="D234" s="4" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E234" s="4" t="n"/>
@@ -11984,7 +11964,7 @@
       </c>
       <c r="D235" s="4" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E235" s="4" t="n"/>
@@ -12033,7 +12013,7 @@
       </c>
       <c r="D236" s="4" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E236" s="4" t="inlineStr">
@@ -12139,7 +12119,7 @@
       </c>
       <c r="D238" s="4" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E238" s="4" t="n"/>
@@ -12188,7 +12168,7 @@
       </c>
       <c r="D239" s="4" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E239" s="4" t="n"/>
@@ -12237,7 +12217,7 @@
       </c>
       <c r="D240" s="4" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E240" s="4" t="n"/>
@@ -12286,7 +12266,7 @@
       </c>
       <c r="D241" s="4" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E241" s="4" t="n"/>
@@ -12376,7 +12356,7 @@
       </c>
       <c r="D243" s="4" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E243" s="4" t="inlineStr">
@@ -12386,7 +12366,7 @@
       </c>
       <c r="F243" s="4" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G243" s="4" t="n"/>
@@ -12433,7 +12413,7 @@
       </c>
       <c r="D244" s="4" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E244" s="4" t="n"/>
@@ -12482,7 +12462,7 @@
       </c>
       <c r="D245" s="4" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E245" s="4" t="inlineStr">
@@ -12492,7 +12472,7 @@
       </c>
       <c r="F245" s="4" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G245" s="4" t="n"/>
@@ -12537,11 +12517,7 @@
           <t>m_barbero</t>
         </is>
       </c>
-      <c r="D246" s="4" t="inlineStr">
-        <is>
-          <t>404</t>
-        </is>
-      </c>
+      <c r="D246" s="4" t="n"/>
       <c r="E246" s="4" t="inlineStr">
         <is>
           <t>veronicambarbero.bsky.social</t>
@@ -12549,7 +12525,7 @@
       </c>
       <c r="F246" s="4" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G246" s="4" t="n"/>
@@ -12647,7 +12623,7 @@
       </c>
       <c r="F248" s="4" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G248" s="4" t="n"/>
@@ -12694,7 +12670,7 @@
       </c>
       <c r="D249" s="4" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E249" s="4" t="n"/>
@@ -12743,7 +12719,7 @@
       </c>
       <c r="D250" s="4" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E250" s="4" t="inlineStr">
@@ -12753,7 +12729,7 @@
       </c>
       <c r="F250" s="4" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G250" s="4" t="n"/>
@@ -12800,7 +12776,7 @@
       </c>
       <c r="D251" s="4" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="E251" s="4" t="n"/>
@@ -12849,7 +12825,7 @@
       </c>
       <c r="D252" s="4" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E252" s="4" t="inlineStr">
@@ -12859,7 +12835,7 @@
       </c>
       <c r="F252" s="4" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G252" s="4" t="n"/>
@@ -12906,7 +12882,7 @@
       </c>
       <c r="D253" s="4" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E253" s="4" t="n"/>
@@ -12955,7 +12931,7 @@
       </c>
       <c r="D254" s="4" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E254" s="4" t="inlineStr">
@@ -12965,7 +12941,7 @@
       </c>
       <c r="F254" s="4" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G254" s="4" t="n"/>
@@ -13053,7 +13029,7 @@
       </c>
       <c r="D256" s="4" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E256" s="4" t="n"/>
@@ -13102,7 +13078,7 @@
       </c>
       <c r="D257" s="4" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E257" s="4" t="n"/>
@@ -13192,7 +13168,7 @@
       </c>
       <c r="D259" s="4" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E259" s="4" t="n"/>
@@ -13241,7 +13217,7 @@
       </c>
       <c r="D260" s="4" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="E260" s="4" t="inlineStr">
@@ -13298,7 +13274,7 @@
       </c>
       <c r="D261" s="4" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E261" s="4" t="inlineStr">
@@ -13396,7 +13372,7 @@
       </c>
       <c r="D263" s="4" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E263" s="4" t="inlineStr">
@@ -13494,7 +13470,7 @@
       </c>
       <c r="D265" s="4" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="E265" s="4" t="n"/>
@@ -13543,7 +13519,7 @@
       </c>
       <c r="D266" s="4" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E266" s="4" t="inlineStr">
@@ -13600,7 +13576,7 @@
       </c>
       <c r="D267" s="4" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E267" s="4" t="n"/>
@@ -13690,7 +13666,7 @@
       </c>
       <c r="D269" s="4" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E269" s="4" t="n"/>
@@ -13878,7 +13854,7 @@
       </c>
       <c r="D273" s="4" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E273" s="4" t="n"/>
@@ -13927,7 +13903,7 @@
       </c>
       <c r="D274" s="4" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E274" s="4" t="n"/>
@@ -13976,7 +13952,7 @@
       </c>
       <c r="D275" s="4" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E275" s="4" t="n"/>
@@ -14070,7 +14046,7 @@
       </c>
       <c r="D277" s="4" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E277" s="4" t="inlineStr">
@@ -14127,7 +14103,7 @@
       </c>
       <c r="D278" s="4" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E278" s="4" t="n"/>
@@ -14174,11 +14150,7 @@
           <t>cristinanarbona</t>
         </is>
       </c>
-      <c r="D279" s="4" t="inlineStr">
-        <is>
-          <t>2026-02-04</t>
-        </is>
-      </c>
+      <c r="D279" s="4" t="n"/>
       <c r="E279" s="4" t="inlineStr">
         <is>
           <t>cristinanarbona.bsky.social</t>
@@ -14233,7 +14205,7 @@
       </c>
       <c r="D280" s="4" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E280" s="4" t="inlineStr">
@@ -14290,7 +14262,7 @@
       </c>
       <c r="D281" s="4" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E281" s="4" t="n"/>
@@ -14339,7 +14311,7 @@
       </c>
       <c r="D282" s="4" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E282" s="4" t="n"/>
@@ -14388,7 +14360,7 @@
       </c>
       <c r="D283" s="4" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E283" s="4" t="n"/>
@@ -14437,7 +14409,7 @@
       </c>
       <c r="D284" s="4" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E284" s="4" t="inlineStr">
@@ -14490,7 +14462,7 @@
       </c>
       <c r="D285" s="4" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E285" s="4" t="inlineStr">
@@ -14588,7 +14560,7 @@
       </c>
       <c r="D287" s="4" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="E287" s="4" t="inlineStr">
@@ -14645,7 +14617,7 @@
       </c>
       <c r="D288" s="4" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E288" s="4" t="n"/>
@@ -14694,7 +14666,7 @@
       </c>
       <c r="D289" s="4" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E289" s="4" t="n"/>
@@ -14743,7 +14715,7 @@
       </c>
       <c r="D290" s="4" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E290" s="4" t="inlineStr">
@@ -14753,7 +14725,7 @@
       </c>
       <c r="F290" s="4" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G290" s="4" t="n"/>
@@ -14882,7 +14854,7 @@
       </c>
       <c r="D293" s="4" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E293" s="4" t="inlineStr">
@@ -14939,7 +14911,7 @@
       </c>
       <c r="D294" s="4" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E294" s="4" t="n"/>
@@ -14988,7 +14960,7 @@
       </c>
       <c r="D295" s="4" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="E295" s="4" t="inlineStr">
@@ -15045,7 +15017,7 @@
       </c>
       <c r="D296" s="4" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E296" s="4" t="n"/>
@@ -15090,7 +15062,7 @@
       </c>
       <c r="D297" s="4" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E297" s="4" t="n"/>
@@ -15139,7 +15111,7 @@
       </c>
       <c r="D298" s="4" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E298" s="4" t="n"/>
@@ -15188,7 +15160,7 @@
       </c>
       <c r="D299" s="4" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E299" s="4" t="n"/>
@@ -15233,7 +15205,7 @@
       </c>
       <c r="D300" s="4" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E300" s="4" t="n"/>
@@ -15282,7 +15254,7 @@
       </c>
       <c r="D301" s="4" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E301" s="4" t="inlineStr">
@@ -15292,7 +15264,7 @@
       </c>
       <c r="F301" s="4" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G301" s="4" t="n"/>
@@ -15339,7 +15311,7 @@
       </c>
       <c r="D302" s="4" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E302" s="4" t="n"/>
@@ -15384,7 +15356,7 @@
       </c>
       <c r="D303" s="4" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E303" s="4" t="n"/>
@@ -15433,7 +15405,7 @@
       </c>
       <c r="D304" s="4" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E304" s="4" t="inlineStr">
@@ -15490,7 +15462,7 @@
       </c>
       <c r="D305" s="4" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E305" s="4" t="n"/>
@@ -15588,7 +15560,7 @@
       </c>
       <c r="D307" s="4" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E307" s="4" t="n"/>
@@ -15637,7 +15609,7 @@
       </c>
       <c r="D308" s="4" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E308" s="4" t="inlineStr">
@@ -15694,7 +15666,7 @@
       </c>
       <c r="D309" s="4" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E309" s="4" t="inlineStr">
@@ -15788,7 +15760,7 @@
       </c>
       <c r="D311" s="4" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E311" s="4" t="n"/>
@@ -15878,7 +15850,7 @@
       </c>
       <c r="D313" s="4" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E313" s="4" t="inlineStr">
@@ -15935,7 +15907,7 @@
       </c>
       <c r="D314" s="4" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E314" s="4" t="inlineStr">
@@ -15945,7 +15917,7 @@
       </c>
       <c r="F314" s="4" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G314" s="4" t="n"/>
@@ -15992,7 +15964,7 @@
       </c>
       <c r="D315" s="4" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E315" s="4" t="n"/>
@@ -16131,7 +16103,7 @@
       </c>
       <c r="D318" s="4" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E318" s="4" t="n"/>
@@ -16180,7 +16152,7 @@
       </c>
       <c r="D319" s="4" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E319" s="4" t="n"/>
@@ -16227,11 +16199,7 @@
           <t>oscarramis</t>
         </is>
       </c>
-      <c r="D320" s="4" t="inlineStr">
-        <is>
-          <t>404</t>
-        </is>
-      </c>
+      <c r="D320" s="4" t="n"/>
       <c r="E320" s="4" t="n"/>
       <c r="F320" s="4" t="n"/>
       <c r="G320" s="4" t="n"/>
@@ -16278,7 +16246,7 @@
       </c>
       <c r="D321" s="4" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E321" s="4" t="inlineStr">
@@ -16288,7 +16256,7 @@
       </c>
       <c r="F321" s="4" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G321" s="4" t="n"/>
@@ -16335,7 +16303,7 @@
       </c>
       <c r="D322" s="4" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E322" s="4" t="inlineStr">
@@ -16441,7 +16409,7 @@
       </c>
       <c r="D324" s="4" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E324" s="4" t="n"/>
@@ -16490,7 +16458,7 @@
       </c>
       <c r="D325" s="4" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E325" s="4" t="inlineStr">
@@ -16547,7 +16515,7 @@
       </c>
       <c r="D326" s="4" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E326" s="4" t="inlineStr">
@@ -16604,7 +16572,7 @@
       </c>
       <c r="D327" s="4" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E327" s="4" t="n"/>
@@ -16653,7 +16621,7 @@
       </c>
       <c r="D328" s="4" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E328" s="4" t="inlineStr">
@@ -16747,7 +16715,7 @@
       </c>
       <c r="D330" s="4" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E330" s="4" t="n"/>
@@ -16796,7 +16764,7 @@
       </c>
       <c r="D331" s="4" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E331" s="4" t="inlineStr">
@@ -16853,7 +16821,7 @@
       </c>
       <c r="D332" s="4" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E332" s="4" t="n"/>
@@ -16902,7 +16870,7 @@
       </c>
       <c r="D333" s="4" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E333" s="4" t="inlineStr">
@@ -16912,7 +16880,7 @@
       </c>
       <c r="F333" s="4" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G333" s="4" t="n"/>
@@ -16959,7 +16927,7 @@
       </c>
       <c r="D334" s="4" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E334" s="4" t="n"/>
@@ -17057,7 +17025,7 @@
       </c>
       <c r="D336" s="4" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E336" s="4" t="inlineStr">
@@ -17067,7 +17035,7 @@
       </c>
       <c r="F336" s="4" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G336" s="4" t="n"/>
@@ -17114,7 +17082,7 @@
       </c>
       <c r="D337" s="4" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E337" s="4" t="n"/>
@@ -17163,7 +17131,7 @@
       </c>
       <c r="D338" s="4" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E338" s="4" t="inlineStr">
@@ -17173,7 +17141,7 @@
       </c>
       <c r="F338" s="4" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G338" s="4" t="n"/>
@@ -17220,7 +17188,7 @@
       </c>
       <c r="D339" s="4" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E339" s="4" t="n"/>
@@ -17269,7 +17237,7 @@
       </c>
       <c r="D340" s="4" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E340" s="4" t="inlineStr">
@@ -17326,7 +17294,7 @@
       </c>
       <c r="D341" s="4" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E341" s="4" t="inlineStr">
@@ -17383,7 +17351,7 @@
       </c>
       <c r="D342" s="4" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E342" s="4" t="inlineStr">
@@ -17393,7 +17361,7 @@
       </c>
       <c r="F342" s="4" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G342" s="4" t="n"/>
@@ -17489,7 +17457,7 @@
       </c>
       <c r="D344" s="4" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E344" s="4" t="n"/>
@@ -17538,7 +17506,7 @@
       </c>
       <c r="D345" s="4" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E345" s="4" t="inlineStr">
@@ -17644,7 +17612,7 @@
       </c>
       <c r="D347" s="4" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E347" s="4" t="n"/>
@@ -17693,7 +17661,7 @@
       </c>
       <c r="D348" s="4" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="E348" s="4" t="n"/>
@@ -17742,7 +17710,7 @@
       </c>
       <c r="D349" s="4" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E349" s="4" t="inlineStr">
@@ -17799,7 +17767,7 @@
       </c>
       <c r="D350" s="4" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E350" s="4" t="inlineStr">
@@ -17852,7 +17820,7 @@
       </c>
       <c r="D351" s="4" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E351" s="4" t="n"/>
@@ -17897,7 +17865,7 @@
       </c>
       <c r="D352" s="4" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E352" s="4" t="n"/>
@@ -17946,7 +17914,7 @@
       </c>
       <c r="D353" s="4" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E353" s="4" t="n"/>
@@ -17995,7 +17963,7 @@
       </c>
       <c r="D354" s="4" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E354" s="4" t="inlineStr">
@@ -18048,7 +18016,7 @@
       </c>
       <c r="D355" s="4" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E355" s="4" t="inlineStr">
@@ -18105,7 +18073,7 @@
       </c>
       <c r="D356" s="4" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E356" s="4" t="n"/>
@@ -18154,7 +18122,7 @@
       </c>
       <c r="D357" s="4" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E357" s="4" t="inlineStr">
@@ -18211,7 +18179,7 @@
       </c>
       <c r="D358" s="4" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E358" s="4" t="n"/>
@@ -18309,7 +18277,7 @@
       </c>
       <c r="D360" s="4" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E360" s="4" t="n"/>
@@ -18358,7 +18326,7 @@
       </c>
       <c r="D361" s="4" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E361" s="4" t="inlineStr">
@@ -18368,7 +18336,7 @@
       </c>
       <c r="F361" s="4" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G361" s="4" t="n"/>
@@ -18464,7 +18432,7 @@
       </c>
       <c r="D363" s="4" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E363" s="4" t="inlineStr">
@@ -18474,7 +18442,7 @@
       </c>
       <c r="F363" s="4" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G363" s="4" t="n"/>
@@ -18521,7 +18489,7 @@
       </c>
       <c r="D364" s="4" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E364" s="4" t="n"/>
@@ -18568,11 +18536,7 @@
           <t>EnriqueSantiago</t>
         </is>
       </c>
-      <c r="D365" s="4" t="inlineStr">
-        <is>
-          <t>2026-02-14</t>
-        </is>
-      </c>
+      <c r="D365" s="4" t="n"/>
       <c r="E365" s="4" t="inlineStr">
         <is>
           <t>enriquesantiago.bsky.social</t>
@@ -18580,7 +18544,7 @@
       </c>
       <c r="F365" s="4" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G365" s="4" t="n"/>
@@ -18668,7 +18632,7 @@
       </c>
       <c r="D367" s="4" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E367" s="4" t="inlineStr">
@@ -18725,7 +18689,7 @@
       </c>
       <c r="D368" s="4" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E368" s="4" t="n"/>
@@ -18823,7 +18787,7 @@
       </c>
       <c r="D370" s="4" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E370" s="4" t="n"/>
@@ -18872,7 +18836,7 @@
       </c>
       <c r="D371" s="4" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E371" s="4" t="n"/>
@@ -18919,11 +18883,7 @@
           <t>dvserrada</t>
         </is>
       </c>
-      <c r="D372" s="4" t="inlineStr">
-        <is>
-          <t>2024-06-13</t>
-        </is>
-      </c>
+      <c r="D372" s="4" t="n"/>
       <c r="E372" s="4" t="n"/>
       <c r="F372" s="4" t="n"/>
       <c r="G372" s="4" t="n"/>
@@ -18970,7 +18930,7 @@
       </c>
       <c r="D373" s="4" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E373" s="4" t="inlineStr">
@@ -19027,7 +18987,7 @@
       </c>
       <c r="D374" s="4" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E374" s="4" t="inlineStr">
@@ -19037,7 +18997,7 @@
       </c>
       <c r="F374" s="4" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G374" s="4" t="n"/>
@@ -19084,7 +19044,7 @@
       </c>
       <c r="D375" s="4" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E375" s="4" t="inlineStr">
@@ -19182,7 +19142,7 @@
       </c>
       <c r="D377" s="4" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E377" s="4" t="inlineStr">
@@ -19192,7 +19152,7 @@
       </c>
       <c r="F377" s="4" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G377" s="4" t="n"/>
@@ -19239,7 +19199,7 @@
       </c>
       <c r="D378" s="4" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E378" s="4" t="inlineStr">
@@ -19249,7 +19209,7 @@
       </c>
       <c r="F378" s="4" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G378" s="4" t="n"/>
@@ -19296,7 +19256,7 @@
       </c>
       <c r="D379" s="4" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E379" s="4" t="n"/>
@@ -19345,7 +19305,7 @@
       </c>
       <c r="D380" s="4" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="E380" s="4" t="n"/>
@@ -19394,7 +19354,7 @@
       </c>
       <c r="D381" s="4" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E381" s="4" t="n"/>
@@ -19490,7 +19450,7 @@
       </c>
       <c r="F383" s="4" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G383" s="4" t="n"/>
@@ -19537,7 +19497,7 @@
       </c>
       <c r="D384" s="4" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E384" s="4" t="n"/>
@@ -19586,7 +19546,7 @@
       </c>
       <c r="D385" s="4" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E385" s="4" t="n"/>
@@ -19635,7 +19595,7 @@
       </c>
       <c r="D386" s="4" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E386" s="4" t="inlineStr">
@@ -19645,7 +19605,7 @@
       </c>
       <c r="F386" s="4" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G386" s="4" t="n"/>
@@ -19690,11 +19650,7 @@
           <t>MARSANCHEZSIERR</t>
         </is>
       </c>
-      <c r="D387" s="4" t="inlineStr">
-        <is>
-          <t>404</t>
-        </is>
-      </c>
+      <c r="D387" s="4" t="n"/>
       <c r="E387" s="4" t="n"/>
       <c r="F387" s="4" t="n"/>
       <c r="G387" s="4" t="n"/>
@@ -19741,7 +19697,7 @@
       </c>
       <c r="D388" s="4" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E388" s="4" t="n"/>
@@ -19790,7 +19746,7 @@
       </c>
       <c r="D389" s="4" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E389" s="4" t="inlineStr">
@@ -19847,7 +19803,7 @@
       </c>
       <c r="D390" s="4" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E390" s="4" t="n"/>
@@ -19896,7 +19852,7 @@
       </c>
       <c r="D391" s="4" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E391" s="4" t="n"/>
@@ -19945,7 +19901,7 @@
       </c>
       <c r="D392" s="4" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E392" s="4" t="n"/>
@@ -20035,7 +19991,7 @@
       </c>
       <c r="D394" s="4" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E394" s="4" t="n"/>
@@ -20084,7 +20040,7 @@
       </c>
       <c r="D395" s="4" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E395" s="4" t="inlineStr">
@@ -20141,7 +20097,7 @@
       </c>
       <c r="D396" s="4" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E396" s="4" t="inlineStr">
@@ -20198,7 +20154,7 @@
       </c>
       <c r="D397" s="4" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E397" s="4" t="n"/>
@@ -20247,7 +20203,7 @@
       </c>
       <c r="D398" s="4" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E398" s="4" t="n"/>
@@ -20296,7 +20252,7 @@
       </c>
       <c r="D399" s="4" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E399" s="4" t="inlineStr">
@@ -20349,7 +20305,7 @@
       </c>
       <c r="D400" s="4" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="E400" s="4" t="n"/>
@@ -20398,7 +20354,7 @@
       </c>
       <c r="D401" s="4" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E401" s="4" t="n"/>
@@ -20496,7 +20452,7 @@
       </c>
       <c r="D403" s="4" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E403" s="4" t="n"/>
@@ -20545,7 +20501,7 @@
       </c>
       <c r="D404" s="4" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E404" s="4" t="n"/>
@@ -20594,7 +20550,7 @@
       </c>
       <c r="D405" s="4" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E405" s="4" t="n"/>
@@ -20643,7 +20599,7 @@
       </c>
       <c r="D406" s="4" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="E406" s="4" t="n"/>
@@ -20692,7 +20648,7 @@
       </c>
       <c r="D407" s="4" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E407" s="4" t="n"/>
@@ -20741,7 +20697,7 @@
       </c>
       <c r="D408" s="4" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E408" s="4" t="n"/>
@@ -20831,7 +20787,7 @@
       </c>
       <c r="D410" s="4" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E410" s="4" t="inlineStr">
@@ -20888,7 +20844,7 @@
       </c>
       <c r="D411" s="4" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E411" s="4" t="inlineStr">
@@ -20898,7 +20854,7 @@
       </c>
       <c r="F411" s="4" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G411" s="4" t="n"/>
@@ -20945,7 +20901,7 @@
       </c>
       <c r="D412" s="4" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E412" s="4" t="n"/>
@@ -20994,7 +20950,7 @@
       </c>
       <c r="D413" s="4" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E413" s="4" t="inlineStr">
@@ -21051,7 +21007,7 @@
       </c>
       <c r="D414" s="4" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E414" s="4" t="inlineStr">
@@ -21108,7 +21064,7 @@
       </c>
       <c r="D415" s="4" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E415" s="4" t="n"/>
@@ -21157,7 +21113,7 @@
       </c>
       <c r="D416" s="4" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E416" s="4" t="n"/>
@@ -21206,7 +21162,7 @@
       </c>
       <c r="D417" s="4" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E417" s="4" t="n"/>
@@ -21255,7 +21211,7 @@
       </c>
       <c r="D418" s="4" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E418" s="4" t="n"/>
@@ -21304,7 +21260,7 @@
       </c>
       <c r="D419" s="5" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E419" s="5" t="n"/>
@@ -21567,7 +21523,7 @@
       </c>
       <c r="D426" s="5" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E426" s="5" t="n"/>
@@ -21682,7 +21638,7 @@
       </c>
       <c r="D429" s="5" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E429" s="5" t="n"/>
@@ -21801,7 +21757,7 @@
       </c>
       <c r="D432" s="5" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E432" s="5" t="n"/>
@@ -21846,7 +21802,7 @@
       </c>
       <c r="D433" s="5" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E433" s="5" t="n"/>
@@ -21919,16 +21875,8 @@
       </c>
       <c r="C435" s="5" t="n"/>
       <c r="D435" s="5" t="n"/>
-      <c r="E435" s="5" t="inlineStr">
-        <is>
-          <t>josearmijogar.bsky.social</t>
-        </is>
-      </c>
-      <c r="F435" s="5" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
+      <c r="E435" s="5" t="n"/>
+      <c r="F435" s="5" t="n"/>
       <c r="G435" s="5" t="n"/>
       <c r="H435" s="5" t="n"/>
       <c r="I435" s="5" t="inlineStr">
@@ -21969,7 +21917,7 @@
       </c>
       <c r="D436" s="5" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E436" s="5" t="inlineStr">
@@ -22022,7 +21970,7 @@
       </c>
       <c r="D437" s="5" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E437" s="5" t="n"/>
@@ -22100,7 +22048,7 @@
       </c>
       <c r="D439" s="5" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E439" s="5" t="n"/>
@@ -22145,7 +22093,7 @@
       </c>
       <c r="D440" s="5" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E440" s="5" t="n"/>
@@ -22190,7 +22138,7 @@
       </c>
       <c r="D441" s="5" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E441" s="5" t="n"/>
@@ -22272,7 +22220,7 @@
       </c>
       <c r="D443" s="5" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E443" s="5" t="n"/>
@@ -22317,7 +22265,7 @@
       </c>
       <c r="D444" s="5" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E444" s="5" t="n"/>
@@ -22399,7 +22347,7 @@
       </c>
       <c r="D446" s="5" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E446" s="5" t="n"/>
@@ -22637,7 +22585,7 @@
       </c>
       <c r="D452" s="5" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E452" s="5" t="n"/>
@@ -22682,7 +22630,7 @@
       </c>
       <c r="D453" s="5" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="E453" s="5" t="n"/>
@@ -22764,7 +22712,7 @@
       </c>
       <c r="D455" s="5" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E455" s="5" t="n"/>
@@ -22879,7 +22827,7 @@
       </c>
       <c r="D458" s="5" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E458" s="5" t="n"/>
@@ -22920,7 +22868,7 @@
       </c>
       <c r="D459" s="5" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E459" s="5" t="inlineStr">
@@ -22973,7 +22921,7 @@
       </c>
       <c r="D460" s="5" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E460" s="5" t="n"/>
@@ -23018,7 +22966,7 @@
       </c>
       <c r="D461" s="5" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E461" s="5" t="inlineStr">
@@ -23515,7 +23463,7 @@
       </c>
       <c r="D474" s="5" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E474" s="5" t="n"/>
@@ -23599,7 +23547,7 @@
       </c>
       <c r="F476" s="5" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G476" s="5" t="n"/>
@@ -23642,7 +23590,7 @@
       </c>
       <c r="D477" s="5" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E477" s="5" t="n"/>
@@ -23687,19 +23635,11 @@
       </c>
       <c r="D478" s="5" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
-        </is>
-      </c>
-      <c r="E478" s="5" t="inlineStr">
-        <is>
-          <t>arianaelena97.bsky.social</t>
-        </is>
-      </c>
-      <c r="F478" s="5" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="E478" s="5" t="n"/>
+      <c r="F478" s="5" t="n"/>
       <c r="G478" s="5" t="n"/>
       <c r="H478" s="5" t="n"/>
       <c r="I478" s="5" t="inlineStr">
@@ -23773,7 +23713,7 @@
       </c>
       <c r="D480" s="5" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E480" s="5" t="n"/>
@@ -23853,7 +23793,7 @@
       </c>
       <c r="F482" s="5" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G482" s="5" t="n"/>
@@ -23896,7 +23836,7 @@
       </c>
       <c r="D483" s="5" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E483" s="5" t="n"/>
@@ -23978,7 +23918,7 @@
       </c>
       <c r="D485" s="5" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="E485" s="5" t="n"/>
@@ -24130,7 +24070,7 @@
       </c>
       <c r="D489" s="5" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E489" s="5" t="inlineStr">
@@ -24212,7 +24152,7 @@
       </c>
       <c r="D491" s="5" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E491" s="5" t="n"/>
@@ -24372,7 +24312,7 @@
       </c>
       <c r="D495" s="5" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E495" s="5" t="inlineStr">
@@ -24458,7 +24398,7 @@
       </c>
       <c r="D497" s="5" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E497" s="5" t="inlineStr">
@@ -24468,7 +24408,7 @@
       </c>
       <c r="F497" s="5" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G497" s="5" t="n"/>
@@ -24626,7 +24566,7 @@
       </c>
       <c r="D501" s="5" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E501" s="5" t="inlineStr">
@@ -24926,7 +24866,7 @@
       </c>
       <c r="D509" s="5" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E509" s="5" t="n"/>
@@ -25201,7 +25141,7 @@
       </c>
       <c r="D516" s="5" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E516" s="5" t="inlineStr">
@@ -25320,7 +25260,7 @@
       </c>
       <c r="D519" s="5" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E519" s="5" t="n"/>
@@ -25449,7 +25389,7 @@
       </c>
       <c r="F522" s="5" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="G522" s="5" t="n"/>
@@ -25529,7 +25469,7 @@
       </c>
       <c r="D524" s="5" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E524" s="5" t="inlineStr">
@@ -25539,7 +25479,7 @@
       </c>
       <c r="F524" s="5" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G524" s="5" t="n"/>
@@ -25730,7 +25670,7 @@
       </c>
       <c r="D529" s="5" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E529" s="5" t="n"/>
@@ -25809,7 +25749,11 @@
           <t>Gil Invernón, Alfonso</t>
         </is>
       </c>
-      <c r="C531" s="5" t="n"/>
+      <c r="C531" s="5" t="inlineStr">
+        <is>
+          <t>alfonsogil</t>
+        </is>
+      </c>
       <c r="D531" s="5" t="n"/>
       <c r="E531" s="5" t="inlineStr">
         <is>
@@ -25818,7 +25762,7 @@
       </c>
       <c r="F531" s="5" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G531" s="5" t="n"/>
@@ -25959,16 +25903,8 @@
       </c>
       <c r="C535" s="5" t="n"/>
       <c r="D535" s="5" t="n"/>
-      <c r="E535" s="5" t="inlineStr">
-        <is>
-          <t>conisco.bsky.social</t>
-        </is>
-      </c>
-      <c r="F535" s="5" t="inlineStr">
-        <is>
-          <t>2026-02-23</t>
-        </is>
-      </c>
+      <c r="E535" s="5" t="n"/>
+      <c r="F535" s="5" t="n"/>
       <c r="G535" s="5" t="n"/>
       <c r="H535" s="5" t="n"/>
       <c r="I535" s="5" t="inlineStr">
@@ -26050,7 +25986,7 @@
       </c>
       <c r="D537" s="5" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E537" s="5" t="n"/>
@@ -26309,7 +26245,7 @@
       </c>
       <c r="D544" s="5" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E544" s="5" t="inlineStr">
@@ -26362,7 +26298,7 @@
       </c>
       <c r="D545" s="5" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="E545" s="5" t="n"/>
@@ -26477,7 +26413,7 @@
       </c>
       <c r="D548" s="5" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="E548" s="5" t="n"/>
@@ -26522,7 +26458,7 @@
       </c>
       <c r="D549" s="5" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E549" s="5" t="n"/>
@@ -26567,7 +26503,7 @@
       </c>
       <c r="D550" s="5" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E550" s="5" t="inlineStr">
@@ -26577,7 +26513,7 @@
       </c>
       <c r="F550" s="5" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G550" s="5" t="n"/>
@@ -26965,7 +26901,7 @@
       </c>
       <c r="D560" s="5" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E560" s="5" t="inlineStr">
@@ -27063,7 +26999,7 @@
       </c>
       <c r="D562" s="5" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E562" s="5" t="n"/>
@@ -27108,7 +27044,7 @@
       </c>
       <c r="D563" s="5" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E563" s="5" t="n"/>
@@ -27190,7 +27126,7 @@
       </c>
       <c r="D565" s="5" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E565" s="5" t="n"/>
@@ -27233,11 +27169,7 @@
           <t>juanlobato_es</t>
         </is>
       </c>
-      <c r="D566" s="5" t="inlineStr">
-        <is>
-          <t>404</t>
-        </is>
-      </c>
+      <c r="D566" s="5" t="n"/>
       <c r="E566" s="5" t="inlineStr">
         <is>
           <t>juanlobato.bsky.social</t>
@@ -27461,7 +27393,7 @@
       </c>
       <c r="D572" s="5" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E572" s="5" t="n"/>
@@ -27506,7 +27438,7 @@
       </c>
       <c r="D573" s="5" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E573" s="5" t="n"/>
@@ -27551,7 +27483,7 @@
       </c>
       <c r="D574" s="5" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E574" s="5" t="n"/>
@@ -27633,7 +27565,7 @@
       </c>
       <c r="D576" s="5" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="E576" s="5" t="n"/>
@@ -27711,7 +27643,7 @@
       </c>
       <c r="D578" s="5" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E578" s="5" t="n"/>
@@ -27937,7 +27869,7 @@
       </c>
       <c r="D584" s="5" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E584" s="5" t="n"/>
@@ -28171,7 +28103,7 @@
       </c>
       <c r="D590" s="5" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E590" s="5" t="n"/>
@@ -28393,7 +28325,7 @@
       </c>
       <c r="D596" s="5" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E596" s="5" t="n"/>
@@ -28656,7 +28588,7 @@
       </c>
       <c r="D603" s="5" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E603" s="5" t="n"/>
@@ -28810,7 +28742,7 @@
       </c>
       <c r="F607" s="5" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G607" s="5" t="n"/>
@@ -28853,7 +28785,7 @@
       </c>
       <c r="D608" s="5" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E608" s="5" t="inlineStr">
@@ -28943,7 +28875,7 @@
       </c>
       <c r="D610" s="5" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E610" s="5" t="inlineStr">
@@ -29078,7 +29010,7 @@
       </c>
       <c r="D613" s="5" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="E613" s="5" t="n"/>
@@ -29118,16 +29050,8 @@
       </c>
       <c r="C614" s="5" t="n"/>
       <c r="D614" s="5" t="n"/>
-      <c r="E614" s="5" t="inlineStr">
-        <is>
-          <t>lludrigueta.bsky.social</t>
-        </is>
-      </c>
-      <c r="F614" s="5" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
+      <c r="E614" s="5" t="n"/>
+      <c r="F614" s="5" t="n"/>
       <c r="G614" s="5" t="n"/>
       <c r="H614" s="5" t="n"/>
       <c r="I614" s="5" t="n"/>
@@ -29456,7 +29380,7 @@
       </c>
       <c r="D623" s="5" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E623" s="5" t="inlineStr">
@@ -29466,7 +29390,7 @@
       </c>
       <c r="F623" s="5" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G623" s="5" t="n"/>
@@ -29632,7 +29556,7 @@
       </c>
       <c r="D627" s="5" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E627" s="5" t="n"/>
@@ -30086,7 +30010,7 @@
       </c>
       <c r="F639" s="5" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G639" s="5" t="n"/>
@@ -30203,7 +30127,7 @@
       </c>
       <c r="D642" s="5" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E642" s="5" t="n"/>
@@ -30408,7 +30332,7 @@
       </c>
       <c r="D647" s="5" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E647" s="5" t="n"/>
@@ -30642,7 +30566,7 @@
       </c>
       <c r="D653" s="5" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E653" s="5" t="inlineStr">
@@ -30941,7 +30865,7 @@
       </c>
       <c r="D660" s="5" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E660" s="5" t="n"/>
@@ -30986,7 +30910,7 @@
       </c>
       <c r="D661" s="5" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E661" s="5" t="inlineStr">
@@ -31039,7 +30963,7 @@
       </c>
       <c r="D662" s="5" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E662" s="5" t="n"/>
@@ -31265,7 +31189,7 @@
       </c>
       <c r="D668" s="5" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E668" s="5" t="n"/>
@@ -31462,7 +31386,7 @@
       </c>
       <c r="D673" s="5" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E673" s="5" t="n"/>
@@ -31610,7 +31534,7 @@
       </c>
       <c r="D677" s="5" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E677" s="5" t="n"/>
@@ -31684,7 +31608,7 @@
       </c>
       <c r="D679" s="5" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E679" s="5" t="inlineStr">
@@ -31840,19 +31764,11 @@
       </c>
       <c r="D683" s="5" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
-        </is>
-      </c>
-      <c r="E683" s="5" t="inlineStr">
-        <is>
-          <t>rosasbishop.bsky.social</t>
-        </is>
-      </c>
-      <c r="F683" s="5" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="E683" s="5" t="n"/>
+      <c r="F683" s="5" t="n"/>
       <c r="G683" s="5" t="n"/>
       <c r="H683" s="5" t="n"/>
       <c r="I683" s="5" t="inlineStr">
@@ -31888,16 +31804,8 @@
       </c>
       <c r="C684" s="5" t="n"/>
       <c r="D684" s="5" t="n"/>
-      <c r="E684" s="5" t="inlineStr">
-        <is>
-          <t>hecsanchez.bsky.social</t>
-        </is>
-      </c>
-      <c r="F684" s="5" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
+      <c r="E684" s="5" t="n"/>
+      <c r="F684" s="5" t="n"/>
       <c r="G684" s="5" t="n"/>
       <c r="H684" s="5" t="n"/>
       <c r="I684" s="5" t="n"/>
@@ -32148,7 +32056,7 @@
       </c>
       <c r="D691" s="5" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E691" s="5" t="n"/>
@@ -32263,7 +32171,7 @@
       </c>
       <c r="D694" s="5" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E694" s="5" t="n"/>
@@ -32468,7 +32376,7 @@
       </c>
       <c r="D699" s="5" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="E699" s="5" t="inlineStr">
@@ -32521,7 +32429,7 @@
       </c>
       <c r="D700" s="5" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E700" s="5" t="n"/>
@@ -32566,7 +32474,7 @@
       </c>
       <c r="D701" s="5" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E701" s="5" t="n"/>
@@ -32611,7 +32519,7 @@
       </c>
       <c r="D702" s="5" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E702" s="5" t="n"/>
@@ -32693,7 +32601,7 @@
       </c>
       <c r="D704" s="5" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E704" s="5" t="n"/>
@@ -32812,7 +32720,7 @@
       </c>
       <c r="D707" s="5" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="E707" s="5" t="n"/>
@@ -32890,7 +32798,7 @@
       </c>
       <c r="D709" s="5" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E709" s="5" t="inlineStr">
@@ -33025,7 +32933,7 @@
       </c>
       <c r="D712" s="5" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E712" s="5" t="n"/>
@@ -33070,7 +32978,7 @@
       </c>
       <c r="D713" s="6" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E713" s="6" t="inlineStr">
@@ -33115,7 +33023,7 @@
       </c>
       <c r="D714" s="6" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E714" s="6" t="inlineStr">
@@ -33125,7 +33033,7 @@
       </c>
       <c r="F714" s="6" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G714" s="6" t="n"/>
@@ -33160,7 +33068,7 @@
       </c>
       <c r="D715" s="6" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E715" s="6" t="n"/>
@@ -33207,7 +33115,7 @@
       </c>
       <c r="F716" s="6" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G716" s="6" t="n"/>
@@ -33242,7 +33150,7 @@
       </c>
       <c r="D717" s="6" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E717" s="6" t="inlineStr">
@@ -33252,7 +33160,7 @@
       </c>
       <c r="F717" s="6" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G717" s="6" t="n"/>
@@ -33287,7 +33195,7 @@
       </c>
       <c r="D718" s="6" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E718" s="6" t="inlineStr">
@@ -33332,7 +33240,7 @@
       </c>
       <c r="D719" s="6" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E719" s="6" t="inlineStr">
@@ -33342,7 +33250,7 @@
       </c>
       <c r="F719" s="6" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G719" s="6" t="n"/>
@@ -33377,7 +33285,7 @@
       </c>
       <c r="D720" s="6" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E720" s="6" t="inlineStr">
@@ -33418,7 +33326,7 @@
       </c>
       <c r="D721" s="6" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E721" s="6" t="n"/>
@@ -33455,7 +33363,7 @@
       </c>
       <c r="D722" s="6" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E722" s="6" t="inlineStr">
@@ -33496,7 +33404,7 @@
       </c>
       <c r="D723" s="6" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E723" s="6" t="inlineStr">
@@ -33506,7 +33414,7 @@
       </c>
       <c r="F723" s="6" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G723" s="6" t="n"/>
@@ -33541,7 +33449,7 @@
       </c>
       <c r="D724" s="6" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E724" s="6" t="inlineStr">
@@ -33551,7 +33459,7 @@
       </c>
       <c r="F724" s="6" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G724" s="6" t="inlineStr">
@@ -33561,7 +33469,7 @@
       </c>
       <c r="H724" s="6" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="I724" s="6" t="inlineStr">
@@ -33594,7 +33502,7 @@
       </c>
       <c r="D725" s="6" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E725" t="inlineStr">
@@ -33639,7 +33547,7 @@
       </c>
       <c r="D726" s="6" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E726" s="6" t="inlineStr">
@@ -33649,7 +33557,7 @@
       </c>
       <c r="F726" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G726" s="6" t="n"/>
@@ -33694,7 +33602,7 @@
       </c>
       <c r="F727" s="6" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G727" s="6" t="n"/>
@@ -33729,7 +33637,7 @@
       </c>
       <c r="D728" s="6" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E728" s="6" t="inlineStr">
@@ -33739,7 +33647,7 @@
       </c>
       <c r="F728" s="6" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G728" s="6" t="n"/>
@@ -33774,7 +33682,7 @@
       </c>
       <c r="D729" s="6" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="E729" s="6" t="inlineStr">
@@ -33819,7 +33727,7 @@
       </c>
       <c r="D730" s="6" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E730" s="6" t="n"/>
@@ -33856,7 +33764,7 @@
       </c>
       <c r="D731" s="6" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E731" s="6" t="n"/>
@@ -33893,7 +33801,7 @@
       </c>
       <c r="D732" s="6" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E732" s="6" t="n"/>
@@ -33930,7 +33838,7 @@
       </c>
       <c r="D733" s="6" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E733" s="6" t="n"/>
@@ -33967,7 +33875,7 @@
       </c>
       <c r="D734" s="6" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E734" s="6" t="inlineStr">
@@ -34012,7 +33920,7 @@
       </c>
       <c r="D735" s="6" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E735" s="6" t="n"/>
@@ -34049,7 +33957,7 @@
       </c>
       <c r="D736" s="6" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E736" s="6" t="inlineStr">
@@ -34094,7 +34002,7 @@
       </c>
       <c r="D737" s="6" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E737" s="6" t="n"/>
@@ -34131,7 +34039,7 @@
       </c>
       <c r="D738" s="6" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E738" s="6" t="n"/>
@@ -34168,7 +34076,7 @@
       </c>
       <c r="D739" s="6" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E739" s="6" t="inlineStr">
@@ -34213,7 +34121,7 @@
       </c>
       <c r="D740" s="6" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="E740" s="6" t="n"/>
@@ -34244,11 +34152,7 @@
           <t>SeAcaboLaFiesta</t>
         </is>
       </c>
-      <c r="D741" s="6" t="inlineStr">
-        <is>
-          <t>404</t>
-        </is>
-      </c>
+      <c r="D741" s="6" t="n"/>
       <c r="E741" s="6" t="n"/>
       <c r="F741" s="6" t="n"/>
       <c r="G741" s="6" t="n"/>
@@ -34283,7 +34187,7 @@
       </c>
       <c r="D742" s="7" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E742" s="7" t="n"/>
@@ -34328,7 +34232,7 @@
       </c>
       <c r="D743" s="7" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E743" s="7" t="inlineStr">
@@ -34377,7 +34281,7 @@
       </c>
       <c r="D744" s="7" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E744" s="7" t="n"/>
@@ -34426,7 +34330,7 @@
       </c>
       <c r="D745" s="7" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E745" s="7" t="inlineStr">
@@ -34475,7 +34379,7 @@
       </c>
       <c r="D746" s="7" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E746" s="7" t="n"/>
@@ -34518,11 +34422,7 @@
           <t>Jorge_Azcon</t>
         </is>
       </c>
-      <c r="D747" s="7" t="inlineStr">
-        <is>
-          <t>2026-02-13</t>
-        </is>
-      </c>
+      <c r="D747" s="7" t="n"/>
       <c r="E747" s="7" t="n"/>
       <c r="F747" s="7" t="n"/>
       <c r="G747" s="7" t="n"/>
@@ -34569,7 +34469,7 @@
       </c>
       <c r="D748" s="7" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E748" s="7" t="inlineStr">
@@ -34618,7 +34518,7 @@
       </c>
       <c r="D749" s="7" t="inlineStr">
         <is>
-          <t>2014-10-19</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E749" s="7" t="n"/>
@@ -34663,7 +34563,7 @@
       </c>
       <c r="D750" s="7" t="inlineStr">
         <is>
-          <t>2023-11-19</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E750" s="7" t="n"/>
@@ -34712,7 +34612,7 @@
       </c>
       <c r="D751" s="7" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E751" s="7" t="n"/>
@@ -34757,7 +34657,7 @@
       </c>
       <c r="D752" s="7" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E752" s="7" t="inlineStr">
@@ -34806,7 +34706,7 @@
       </c>
       <c r="D753" s="7" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E753" s="7" t="n"/>
@@ -34855,7 +34755,7 @@
       </c>
       <c r="D754" s="7" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E754" s="7" t="n"/>
@@ -34900,7 +34800,7 @@
       </c>
       <c r="D755" s="7" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E755" s="7" t="inlineStr">
@@ -34949,7 +34849,7 @@
       </c>
       <c r="D756" s="7" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E756" s="7" t="n"/>
@@ -34998,7 +34898,7 @@
       </c>
       <c r="D757" s="7" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E757" s="7" t="inlineStr">
@@ -35047,7 +34947,7 @@
       </c>
       <c r="D758" s="7" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E758" s="7" t="inlineStr">
@@ -35057,7 +34957,7 @@
       </c>
       <c r="F758" s="7" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G758" s="7" t="n"/>
@@ -35100,7 +35000,7 @@
       </c>
       <c r="D759" s="7" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E759" s="7" t="n"/>
@@ -35149,7 +35049,7 @@
       </c>
       <c r="D760" s="7" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E760" s="7" t="n"/>
@@ -35194,7 +35094,7 @@
       </c>
       <c r="D761" s="7" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E761" s="7" t="n"/>
@@ -35239,7 +35139,7 @@
       </c>
       <c r="D762" s="7" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E762" s="7" t="inlineStr">
@@ -35382,7 +35282,7 @@
       </c>
       <c r="D765" s="7" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E765" s="7" t="n"/>
@@ -35431,7 +35331,7 @@
       </c>
       <c r="D766" s="7" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E766" s="7" t="n"/>
@@ -35476,7 +35376,7 @@
       </c>
       <c r="D767" s="7" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E767" s="7" t="inlineStr">
@@ -35523,11 +35423,7 @@
           <t>mariachivite</t>
         </is>
       </c>
-      <c r="D768" s="7" t="inlineStr">
-        <is>
-          <t>404</t>
-        </is>
-      </c>
+      <c r="D768" s="7" t="n"/>
       <c r="E768" s="7" t="n"/>
       <c r="F768" s="7" t="n"/>
       <c r="G768" s="7" t="n"/>
@@ -35574,7 +35470,7 @@
       </c>
       <c r="D769" s="7" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E769" s="7" t="n"/>
@@ -35619,7 +35515,7 @@
       </c>
       <c r="D770" s="7" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E770" s="7" t="inlineStr">
@@ -35668,7 +35564,7 @@
       </c>
       <c r="D771" s="7" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E771" s="7" t="n"/>
@@ -35717,7 +35613,7 @@
       </c>
       <c r="D772" s="7" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E772" s="7" t="n"/>
@@ -35762,7 +35658,7 @@
       </c>
       <c r="D773" s="7" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E773" s="7" t="inlineStr">
@@ -35909,7 +35805,7 @@
       </c>
       <c r="D776" s="7" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E776" s="7" t="n"/>
@@ -35954,7 +35850,7 @@
       </c>
       <c r="D777" s="7" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E777" s="7" t="n"/>
@@ -36003,7 +35899,7 @@
       </c>
       <c r="D778" s="7" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E778" s="7" t="n"/>
@@ -36048,7 +35944,7 @@
       </c>
       <c r="D779" s="7" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E779" s="7" t="n"/>
@@ -36093,7 +35989,7 @@
       </c>
       <c r="D780" s="7" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E780" s="7" t="n"/>
@@ -36142,7 +36038,7 @@
       </c>
       <c r="D781" s="7" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E781" s="7" t="n"/>
@@ -36187,7 +36083,7 @@
       </c>
       <c r="D782" s="7" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E782" s="7" t="n"/>
@@ -36232,7 +36128,7 @@
       </c>
       <c r="D783" s="7" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E783" s="7" t="inlineStr">
@@ -36289,7 +36185,7 @@
       </c>
       <c r="D784" s="7" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="E784" s="7" t="n"/>
@@ -36334,7 +36230,7 @@
       </c>
       <c r="D785" s="7" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E785" s="7" t="inlineStr">
@@ -36477,7 +36373,7 @@
       </c>
       <c r="D788" s="7" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E788" s="7" t="inlineStr">
@@ -36526,7 +36422,7 @@
       </c>
       <c r="D789" s="7" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E789" s="7" t="n"/>
@@ -36575,7 +36471,7 @@
       </c>
       <c r="D790" s="7" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E790" s="7" t="n"/>
@@ -36620,7 +36516,7 @@
       </c>
       <c r="D791" s="7" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E791" s="7" t="n"/>
@@ -36665,7 +36561,7 @@
       </c>
       <c r="D792" s="7" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E792" s="7" t="inlineStr">
@@ -36675,7 +36571,7 @@
       </c>
       <c r="F792" s="7" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G792" s="7" t="n"/>
@@ -36722,7 +36618,7 @@
       </c>
       <c r="D793" s="7" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E793" s="7" t="n"/>
@@ -36767,7 +36663,7 @@
       </c>
       <c r="D794" s="7" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E794" s="7" t="inlineStr">
@@ -36820,7 +36716,7 @@
       </c>
       <c r="D795" s="7" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E795" s="7" t="inlineStr">
@@ -36922,7 +36818,7 @@
       </c>
       <c r="D797" s="7" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E797" s="7" t="inlineStr">
@@ -36975,7 +36871,7 @@
       </c>
       <c r="D798" s="7" t="inlineStr">
         <is>
-          <t>2018-01-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E798" s="7" t="n"/>
@@ -37024,7 +36920,7 @@
       </c>
       <c r="D799" s="8" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E799" s="8" t="inlineStr">
@@ -37034,7 +36930,7 @@
       </c>
       <c r="F799" s="8" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G799" s="8" t="n"/>
@@ -37073,7 +36969,7 @@
       </c>
       <c r="D800" s="8" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E800" s="8" t="inlineStr">
@@ -37118,7 +37014,7 @@
       </c>
       <c r="D801" s="8" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E801" s="8" t="inlineStr">
@@ -37128,7 +37024,7 @@
       </c>
       <c r="F801" s="8" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="G801" s="8" t="n"/>
@@ -37167,7 +37063,7 @@
       </c>
       <c r="D802" s="8" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E802" s="8" t="n"/>
@@ -37208,7 +37104,7 @@
       </c>
       <c r="D803" s="8" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="E803" s="8" t="n"/>
@@ -37249,7 +37145,7 @@
       </c>
       <c r="D804" s="8" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E804" s="8" t="inlineStr">
@@ -37294,7 +37190,7 @@
       </c>
       <c r="D805" s="8" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E805" s="8" t="inlineStr">
@@ -37345,7 +37241,7 @@
       </c>
       <c r="F806" s="8" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G806" s="8" t="n"/>
@@ -37384,7 +37280,7 @@
       </c>
       <c r="D807" s="8" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E807" s="8" t="n"/>
@@ -37425,7 +37321,7 @@
       </c>
       <c r="D808" s="8" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E808" s="8" t="inlineStr">
@@ -37435,7 +37331,7 @@
       </c>
       <c r="F808" s="8" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G808" s="8" t="n"/>
@@ -37474,7 +37370,7 @@
       </c>
       <c r="D809" s="8" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E809" s="8" t="inlineStr">
@@ -37519,7 +37415,7 @@
       </c>
       <c r="D810" s="8" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E810" s="8" t="inlineStr">
@@ -37529,7 +37425,7 @@
       </c>
       <c r="F810" s="8" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G810" s="8" t="n"/>
@@ -37568,7 +37464,7 @@
       </c>
       <c r="D811" s="8" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E811" s="8" t="inlineStr">
@@ -37617,7 +37513,7 @@
       </c>
       <c r="D812" s="8" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="E812" s="8" t="inlineStr">
@@ -37627,7 +37523,7 @@
       </c>
       <c r="F812" s="8" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G812" s="8" t="n"/>
@@ -37666,7 +37562,7 @@
       </c>
       <c r="D813" s="8" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E813" s="8" t="inlineStr">
@@ -37711,7 +37607,7 @@
       </c>
       <c r="D814" s="8" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E814" s="8" t="inlineStr">
@@ -37760,7 +37656,7 @@
       </c>
       <c r="D815" s="8" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E815" s="8" t="n"/>
@@ -37801,7 +37697,7 @@
       </c>
       <c r="D816" s="8" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E816" s="8" t="inlineStr">
@@ -37811,7 +37707,7 @@
       </c>
       <c r="F816" s="8" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G816" s="8" t="n"/>
@@ -37850,7 +37746,7 @@
       </c>
       <c r="D817" s="8" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E817" s="8" t="inlineStr">
@@ -37905,7 +37801,7 @@
       </c>
       <c r="F818" s="8" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G818" s="8" t="n"/>
@@ -37944,7 +37840,7 @@
       </c>
       <c r="D819" s="8" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E819" s="8" t="n"/>
@@ -37985,7 +37881,7 @@
       </c>
       <c r="D820" s="8" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E820" s="8" t="inlineStr">
@@ -37995,7 +37891,7 @@
       </c>
       <c r="F820" s="8" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G820" s="8" t="n"/>
@@ -38034,7 +37930,7 @@
       </c>
       <c r="D821" s="8" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E821" s="8" t="inlineStr">
@@ -38083,7 +37979,7 @@
       </c>
       <c r="D822" s="8" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E822" s="8" t="inlineStr">
@@ -38093,7 +37989,7 @@
       </c>
       <c r="F822" s="8" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G822" s="8" t="n"/>
@@ -38132,7 +38028,7 @@
       </c>
       <c r="D823" s="8" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E823" s="8" t="inlineStr">
@@ -38177,7 +38073,7 @@
       </c>
       <c r="D824" s="8" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E824" s="8" t="inlineStr">
@@ -38220,11 +38116,7 @@
           <t>ULPGC</t>
         </is>
       </c>
-      <c r="D825" s="8" t="inlineStr">
-        <is>
-          <t>404</t>
-        </is>
-      </c>
+      <c r="D825" s="8" t="n"/>
       <c r="E825" s="8" t="inlineStr">
         <is>
           <t>ulpgc.es</t>
@@ -38232,7 +38124,7 @@
       </c>
       <c r="F825" s="8" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G825" s="8" t="n"/>
@@ -38271,7 +38163,7 @@
       </c>
       <c r="D826" s="8" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E826" s="8" t="n"/>
@@ -38312,7 +38204,7 @@
       </c>
       <c r="D827" s="8" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E827" s="8" t="inlineStr">
@@ -38322,7 +38214,7 @@
       </c>
       <c r="F827" s="8" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G827" s="8" t="n"/>
@@ -38361,7 +38253,7 @@
       </c>
       <c r="D828" s="8" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E828" s="8" t="inlineStr">
@@ -38371,7 +38263,7 @@
       </c>
       <c r="F828" s="8" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G828" s="8" t="n"/>
@@ -38420,7 +38312,7 @@
       </c>
       <c r="F829" s="8" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G829" s="8" t="n"/>
@@ -38459,7 +38351,7 @@
       </c>
       <c r="D830" s="8" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E830" s="8" t="inlineStr">
@@ -38514,7 +38406,7 @@
       </c>
       <c r="F831" s="8" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G831" s="8" t="n"/>
@@ -38551,11 +38443,7 @@
           <t>uva_es</t>
         </is>
       </c>
-      <c r="D832" s="8" t="inlineStr">
-        <is>
-          <t>2026-02-13</t>
-        </is>
-      </c>
+      <c r="D832" s="8" t="n"/>
       <c r="E832" s="8" t="inlineStr">
         <is>
           <t>uva-es.bsky.social</t>
@@ -38563,7 +38451,7 @@
       </c>
       <c r="F832" s="8" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G832" s="8" t="n"/>
@@ -38612,7 +38500,7 @@
       </c>
       <c r="F833" s="8" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G833" s="8" t="n"/>
@@ -38661,7 +38549,7 @@
       </c>
       <c r="F834" s="8" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G834" s="8" t="n"/>
@@ -38710,7 +38598,7 @@
       </c>
       <c r="F835" s="8" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G835" s="8" t="n"/>
@@ -38759,7 +38647,7 @@
       </c>
       <c r="F836" s="8" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G836" s="8" t="n"/>
@@ -38798,7 +38686,7 @@
       </c>
       <c r="D837" s="8" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E837" s="8" t="inlineStr">
@@ -38808,7 +38696,7 @@
       </c>
       <c r="F837" s="8" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G837" s="8" t="n"/>
@@ -38857,7 +38745,7 @@
       </c>
       <c r="F838" s="8" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G838" s="8" t="n"/>
@@ -38906,7 +38794,7 @@
       </c>
       <c r="F839" s="8" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G839" s="8" t="n"/>
@@ -38994,7 +38882,7 @@
       </c>
       <c r="D841" s="8" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E841" s="8" t="inlineStr">
@@ -39039,7 +38927,7 @@
       </c>
       <c r="D842" s="8" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="E842" s="8" t="inlineStr">
@@ -39049,7 +38937,7 @@
       </c>
       <c r="F842" s="8" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G842" s="8" t="n"/>
@@ -39088,7 +38976,7 @@
       </c>
       <c r="D843" s="8" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E843" s="8" t="inlineStr">
@@ -39098,7 +38986,7 @@
       </c>
       <c r="F843" s="8" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G843" s="8" t="n"/>
@@ -39147,7 +39035,7 @@
       </c>
       <c r="F844" s="8" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G844" s="8" t="n"/>
@@ -39196,7 +39084,7 @@
       </c>
       <c r="F845" s="8" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G845" s="8" t="n"/>
@@ -39235,7 +39123,7 @@
       </c>
       <c r="D846" s="8" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E846" s="8" t="inlineStr">
@@ -39245,7 +39133,7 @@
       </c>
       <c r="F846" s="8" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G846" s="8" t="n"/>
@@ -39284,7 +39172,7 @@
       </c>
       <c r="D847" s="8" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E847" s="8" t="inlineStr">
@@ -39294,7 +39182,7 @@
       </c>
       <c r="F847" s="8" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G847" s="8" t="n"/>
@@ -39343,7 +39231,7 @@
       </c>
       <c r="F848" s="8" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G848" s="8" t="n"/>
